--- a/stories/arbres/ATOM-TMP.SEM.002-05.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Diane est à la cuisine. Papa accroche un calendrier. Papa dit : lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Diane reste à la maison. Elle joue avec papa. Samedi, Diane reste aussi. Dimanche encore. Papa dit : samedi et dimanche, c'est le week-end. Diane touche mercredi. Elle touche samedi. Elle touche dimanche. Papa dit : mercredi, samedi, dimanche, on est à la maison.</t>
+          <t>Diane est à la cuisine. Papa accroche un calendrier. Lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Diane reste à la maison. Elle joue avec papa. Samedi, Diane reste aussi. Dimanche encore. Samedi et dimanche, c'est le week-end. Diane touche mercredi. Elle touche samedi. Elle touche dimanche. Mercredi, samedi, dimanche, on est à la maison.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Diane est à la cuisine. Papa accroche un calendrier.
+papa|Lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Diane reste à la maison. Elle joue avec papa. Samedi, Diane reste aussi. Dimanche encore.
+papa|Samedi et dimanche, c'est le week-end.
+narrateur|Diane touche mercredi. Elle touche samedi. Elle touche dimanche.
+papa|Mercredi, samedi, dimanche, on est à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Diane est à la maison le mercredi. Quels autres jours aussi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Diane a nommé mercredi. Elle a nommé samedi et dimanche. C'est le week-end.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le crayon. Diane dessine.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.002-05.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 papa|Mercredi, samedi, dimanche, on est à la maison.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Diane est à la maison le mercredi. Quels autres jours aussi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Diane a nommé mercredi. Elle a nommé samedi et dimanche. C'est le week-end.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Papa range le crayon. Diane dessine.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.SEM.002-05.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Diane nomme mercredi et le week-end</t>
+          <t>La farine et le vent</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina veut un gâteau, puis le cerf-volant. Mercredi, la farine fait un nuage. Ils essuient. Dimanche, week-end, le vent prend enfin la toile.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Diane est à la cuisine. Papa accroche un calendrier. Lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Diane reste à la maison. Elle joue avec papa. Samedi, Diane reste aussi. Dimanche encore. Samedi et dimanche, c'est le week-end. Diane touche mercredi. Elle touche samedi. Elle touche dimanche. Mercredi, samedi, dimanche, on est à la maison.</t>
+          <t>La farine a fait un nuage blanc. Elle retombe sur le bois de la table. Ça sent le beurre tiède, déjà. C'est mercredi, Nina. Pas d'école. On fait le gâteau ? Oui. Pour dimanche. Le cerf-volant aussi ? Dimanche, s'il y a du vent. Samedi et dimanche, c'est le week-end. Nina verse encore un peu de farine. Le nuage revient, plus petit. Oh. Trop d'un coup. On essuie ? Oui. En ce moment, Nina passe le linge. La farine part en traînées blanches. Tu fais une place nette. Pour le bol. Pour le bol. Le bol est lourd, en terre. Nina le pose sans le faire sonner. Bien. L'œuf maintenant. L'œuf casse net. Le jaune tient, puis glisse. Il est orange. Comme le cerf-volant. Le grand. Le grand, dimanche. Ils mélangent. La pâte devient collante, puis lisse. Tu veux lécher la cuillère ? Un peu. C'est sucré, un peu rêche encore. Mercredi, on cuit. Samedi, il sera froid. Dimanche, le vent. Pas d'école. Pas d'école. Comme mercredi. Le four souffle un air chaud. Nina s'éloigne d'un pas. On regarde par la vitre. Il gonfle. Il gonfle. Une miette de farine reste sur le nez de Nina. Là. Papa l'essuie du pouce. Merci. Merci d'avoir essuyé la table.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Diane est à la cuisine. Papa accroche un calendrier. Papa dit : lundi, mardi, jeudi, vendredi, c'est l'école. &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;, Diane reste à la maison. Elle joue avec papa. Samedi, Diane reste aussi. Dimanche encore. Papa dit : samedi et dimanche, c'est le week-end. Diane touche mercredi. Elle touche samedi. Elle touche dimanche. Papa dit : mercredi, samedi, dimanche, on est à la maison.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La farine a fait un nuage blanc. Elle retombe sur le bois de la table. Ça sent le beurre tiède, déjà. C'est mercredi, Nina. Pas d'école. On fait le gâteau ? Oui. Pour dimanche. Le cerf-volant aussi ? Dimanche, s'il y a du vent. Samedi et dimanche, c'est le week-end. Nina verse encore un peu de farine. Le nuage revient, plus petit. Oh. Trop d'un coup. On essuie ? Oui. En ce moment, Nina passe le linge. La farine part en traînées blanches. Tu fais une place nette. Pour le bol. Pour le bol. Le bol est lourd, en terre. Nina le pose sans le faire sonner. Bien. L'œuf maintenant. L'œuf casse net. Le jaune tient, puis glisse. Il est orange. Comme le cerf-volant. Le grand. Le grand, dimanche. Ils mélangent. La pâte devient collante, puis lisse. Tu veux lécher la cuillère ? Un peu. C'est sucré, un peu rêche encore. Mercredi, on cuit. Samedi, il sera froid. Dimanche, le vent. Pas d'école. Pas d'école. Comme mercredi. Le four souffle un air chaud. Nina s'éloigne d'un pas. On regarde par la vitre. Il gonfle. Il gonfle. Une miette de farine reste sur le nez de Nina. Là. Papa l'essuie du pouce. Merci. Merci d'avoir essuyé la table.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,61 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Diane est à la cuisine. Papa accroche un calendrier.
-papa|Lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Diane reste à la maison. Elle joue avec papa. Samedi, Diane reste aussi. Dimanche encore.
+          <t>narrateur|La farine a fait un nuage blanc.
+narrateur|Elle retombe sur le bois de la table.
+narrateur|Ça sent le beurre tiède, déjà.
+papa|C'est mercredi, Nina.
+papa|Pas d'école.
+enfant-f|On fait le gâteau ?
+papa|Oui.
+papa|Pour dimanche.
+enfant-f|Le cerf-volant aussi ?
+papa|Dimanche, s'il y a du vent.
 papa|Samedi et dimanche, c'est le week-end.
-narrateur|Diane touche mercredi. Elle touche samedi. Elle touche dimanche.
-papa|Mercredi, samedi, dimanche, on est à la maison.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Nina verse encore un peu de farine.
+narrateur|Le nuage revient, plus petit.
+enfant-f|Oh.
+papa|Trop d'un coup.
+papa|On essuie ?
+enfant-f|Oui.
+narrateur|En ce moment, Nina passe le linge.
+narrateur|La farine part en traînées blanches.
+papa|Tu fais une place nette.
+enfant-f|Pour le bol.
+papa|Pour le bol.
+narrateur|Le bol est lourd, en terre.
+narrateur|Nina le pose sans le faire sonner.
+papa|Bien.
+papa|L'œuf maintenant.
+narrateur|L'œuf casse net.
+narrateur|Le jaune tient, puis glisse.
+enfant-f|Il est orange.
+papa|Comme le cerf-volant.
+enfant-f|Le grand.
+papa|Le grand, dimanche.
+narrateur|Ils mélangent.
+narrateur|La pâte devient collante, puis lisse.
+papa|Tu veux lécher la cuillère ?
+enfant-f|Un peu.
+narrateur|C'est sucré, un peu rêche encore.
+papa|Mercredi, on cuit.
+papa|Samedi, il sera froid.
+papa|Dimanche, le vent.
+enfant-f|Pas d'école.
+papa|Pas d'école.
+papa|Comme mercredi.
+narrateur|Le four souffle un air chaud.
+narrateur|Nina s'éloigne d'un pas.
+papa|On regarde par la vitre.
+enfant-f|Il gonfle.
+papa|Il gonfle.
+narrateur|Une miette de farine reste sur le nez de Nina.
+papa|Là.
+narrateur|Papa l'essuie du pouce.
+enfant-f|Merci.
+papa|Merci d'avoir essuyé la table.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,12 +1403,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Diane est à la maison le mercredi. Quels autres jours aussi ?</t>
+          <t>Quels autres jours, comme mercredi, sans l'école ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Diane est à la maison le &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;. Quels autres jours aussi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Quels autres jours, comme mercredi, sans l'école ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1364,7 +1423,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>samedi | dimanche | week-end | mercredi</t>
+          <t>week-end | weekend | samedi | dimanche | le week-end | mercredi</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1421,14 +1480,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1504,10 +1563,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Diane est à la maison le mercredi. Quels autres jours aussi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Quels autres jours, comme mercredi, sans l'école ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,12 +1590,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Diane a nommé mercredi. Elle a nommé samedi et dimanche. C'est le week-end.</t>
+          <t>Nina sent encore le beurre sur ses doigts. Samedi. Dimanche. Oui. C'est le week-end. Le gâteau, puis le vent. Le cerf-volant. Dimanche. Le gâteau dore derrière la vitre. Une bulle se fige au milieu. Tu as versé trop vite, puis tu as essuyé. Bravo. Le nuage est parti. La table est nette. On attend qu'il descende ? Oui, papa. La cuisine sent le chaud et le sucre. Le linge blanc a une trace de farine.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Diane a nommé &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;. Elle a nommé samedi et dimanche. C'est le week-end.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina sent encore le beurre sur ses doigts. Samedi. Dimanche. Oui. C'est le week-end. Le gâteau, puis le vent. Le cerf-volant. Dimanche. Le gâteau dore derrière la vitre. Une bulle se fige au milieu. Tu as versé trop vite, puis tu as essuyé. Bravo. Le nuage est parti. La table est nette. On attend qu'il descende ? Oui, papa. La cuisine sent le chaud et le sucre. Le linge blanc a une trace de farine.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1600,7 +1658,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1676,10 +1734,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Diane a nommé mercredi. Elle a nommé samedi et dimanche. C'est le week-end.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina sent encore le beurre sur ses doigts.
+enfant-f|Samedi.
+enfant-f|Dimanche.
+papa|Oui.
+papa|C'est le week-end.
+papa|Le gâteau, puis le vent.
+enfant-f|Le cerf-volant.
+papa|Dimanche.
+narrateur|Le gâteau dore derrière la vitre.
+narrateur|Une bulle se fige au milieu.
+papa|Tu as versé trop vite, puis tu as essuyé.
+papa|Bravo.
+enfant-f|Le nuage est parti.
+papa|La table est nette.
+papa|On attend qu'il descende ?
+enfant-f|Oui, papa.
+narrateur|La cuisine sent le chaud et le sucre.
+narrateur|Le linge blanc a une trace de farine.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,12 +1778,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le crayon. Diane dessine.</t>
+          <t>Dimanche, le vent tire déjà les herbes. Nina tient le gâteau dans un linge. Une part pour après. Après le ciel. Le cerf-volant orange claque une fois. Le fil brûle un peu la main, puis non. Tu cours dans l'herbe ? Dans l'herbe. La toile s'élève. Elle penche, puis elle tient. Il vole ! Comme mercredi le gâteau a gonflé. C'est le week-end. Samedi il était froid. Et dimanche il y a le vent. Tu tiens bien le fil ? Oui. Une miette sucrée reste au coin de la bouche. Le ciel tire l'orange tout en haut.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range le crayon. Diane dessine.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Dimanche, le vent tire déjà les herbes. Nina tient le gâteau dans un linge. Une part pour après. Après le ciel. Le cerf-volant orange claque une fois. Le fil brûle un peu la main, puis non. Tu cours dans l'herbe ? Dans l'herbe. La toile s'élève. Elle penche, puis elle tient. Il vole ! Comme mercredi le gâteau a gonflé. C'est le week-end. Samedi il était froid. Et dimanche il y a le vent. Tu tiens bien le fil ? Oui. Une miette sucrée reste au coin de la bouche. Le ciel tire l'orange tout en haut.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1772,7 +1846,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1840,10 +1914,27 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le crayon. Diane dessine.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Dimanche, le vent tire déjà les herbes.
+narrateur|Nina tient le gâteau dans un linge.
+enfant-f|Une part pour après.
+papa|Après le ciel.
+narrateur|Le cerf-volant orange claque une fois.
+narrateur|Le fil brûle un peu la main, puis non.
+papa|Tu cours dans l'herbe ?
+enfant-f|Dans l'herbe.
+narrateur|La toile s'élève.
+narrateur|Elle penche, puis elle tient.
+enfant-f|Il vole !
+papa|Comme mercredi le gâteau a gonflé.
+papa|C'est le week-end.
+enfant-f|Samedi il était froid.
+papa|Et dimanche il y a le vent.
+papa|Tu tiens bien le fil ?
+enfant-f|Oui.
+narrateur|Une miette sucrée reste au coin de la bouche.
+narrateur|Le ciel tire l'orange tout en haut.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,12 +1959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le cerf-volant tient. Le gâteau aussi, dans le linge. L'orange claque au-dessus de l'herbe. Le fil vibre un peu entre les doigts. Le vent sent encore le sucre du gâteau.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le cerf-volant tient. Le gâteau aussi, dans le linge. L'orange claque au-dessus de l'herbe. Le fil vibre un peu entre les doigts. Le vent sent encore le sucre du gâteau.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1936,7 +2027,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2008,10 +2099,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|Le cerf-volant tient.
+papa|Le gâteau aussi, dans le linge.
+narrateur|L'orange claque au-dessus de l'herbe.
+narrateur|Le fil vibre un peu entre les doigts.
+narrateur|Le vent sent encore le sucre du gâteau.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2162,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.002-05.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine mercredi, colline dimanche</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Diane, papa</t>
+          <t>Nina, papa</t>
         </is>
       </c>
     </row>
